--- a/assets/modelos_importacao/modelo_importacao_cbo.xlsx
+++ b/assets/modelos_importacao/modelo_importacao_cbo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alcidesdiogenes\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alcidesdiogenes\Desktop\Projetos\ferramentas-dp\assets\modelos_importacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0134D9B-0001-4B83-A79A-3D6789F6C88F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2429C7F-62E4-40FD-961F-F918A048E488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42632266-C8D1-4E99-8617-BC70E36B0764}"/>
+    <workbookView xWindow="-21720" yWindow="1305" windowWidth="21840" windowHeight="13020" xr2:uid="{42632266-C8D1-4E99-8617-BC70E36B0764}"/>
   </bookViews>
   <sheets>
     <sheet name="cbo_escolaridade_estruturado" sheetId="1" r:id="rId1"/>

--- a/assets/modelos_importacao/modelo_importacao_cbo.xlsx
+++ b/assets/modelos_importacao/modelo_importacao_cbo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alcidesdiogenes\Desktop\Projetos\ferramentas-dp\assets\modelos_importacao\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2429C7F-62E4-40FD-961F-F918A048E488}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7975E55A-0E5D-4CF7-ADEA-B105974038FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21720" yWindow="1305" windowWidth="21840" windowHeight="13020" xr2:uid="{42632266-C8D1-4E99-8617-BC70E36B0764}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42632266-C8D1-4E99-8617-BC70E36B0764}"/>
   </bookViews>
   <sheets>
     <sheet name="cbo_escolaridade_estruturado" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>CBO</t>
   </si>
@@ -40,10 +40,13 @@
     <t>Titulo</t>
   </si>
   <si>
-    <t>Caso sim, colocar "sim"</t>
+    <t>Caso seja, colocar "sim"</t>
   </si>
   <si>
-    <t>Cargo de confiança</t>
+    <t>Colaborador</t>
+  </si>
+  <si>
+    <t>Cargo de confiança/formação tecnica/aprendiz</t>
   </si>
 </sst>
 </file>
@@ -554,7 +557,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -566,6 +569,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -943,16 +949,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED846F37-B85F-49D9-9751-C80706BDC9EF}">
-  <dimension ref="A1:C105"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="44.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.6640625" customWidth="1"/>
-    <col min="3" max="3" width="23.77734375" customWidth="1"/>
+    <col min="3" max="3" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1"/>
@@ -960,8 +967,8 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1"/>
@@ -969,10 +976,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -982,69 +989,75 @@
       <c r="C4" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="D4" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>519110</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>784205</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>521140</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>422105</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>391205</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>784205</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>514320</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>840105</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>411005</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>514320</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>784205</v>
       </c>
